--- a/output/pdf_financials_xlsx/PTFY.xlsx
+++ b/output/pdf_financials_xlsx/PTFY.xlsx
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.047191</v>
+        <v>-0.047191</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.052649</v>
+        <v>-0.052649</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.094</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.047191</v>
+        <v>-0.047191</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.052649</v>
+        <v>-0.052649</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.094</v>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.047191</v>
+        <v>-0.047191</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.052649</v>
+        <v>-0.052649</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.094</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.658112</v>
+        <v>0.658112</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>36.466667</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.047191</v>
+        <v>-0.047191</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.052649</v>
+        <v>-0.052649</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.094</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.047191</v>
+        <v>-0.047191</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.052649</v>
+        <v>-0.052649</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.05</v>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3071,16 +3071,16 @@
         <v>1.161</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>3.992</v>
+        <v>5.411</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>6.456</v>
+        <v>7.875</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>9.726000000000001</v>
+        <v>10.303</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>9.726000000000001</v>
+        <v>10.303</v>
       </c>
     </row>
     <row r="93">
@@ -5882,7 +5882,11 @@
           <t>Share purchase warrants reserve 577</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -7325,7 +7329,11 @@
           <t>Share purchase warrants reserve</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -8486,7 +8494,11 @@
           <t>Share purchase warrants reserve</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -18754,16 +18766,16 @@
         </is>
       </c>
       <c r="E285" s="5" t="n">
-        <v>0.047191</v>
+        <v>-0.047191</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>0.052649</v>
+        <v>-0.052649</v>
       </c>
       <c r="G285" s="5" t="n">
-        <v>0.082581</v>
+        <v>-0.082581</v>
       </c>
       <c r="H285" s="5" t="n">
-        <v>0.187135</v>
+        <v>-0.187135</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PTFY.xlsx
+++ b/output/pdf_financials_xlsx/PTFY.xlsx
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0887</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.321073</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.114</v>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0887</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.321073</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.114</v>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">

--- a/output/pdf_financials_xlsx/PTFY.xlsx
+++ b/output/pdf_financials_xlsx/PTFY.xlsx
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="116">
@@ -10291,7 +10291,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
